--- a/data/kpi-history.xlsx
+++ b/data/kpi-history.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C349"/>
+  <dimension ref="A1:C350"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -4973,6 +4973,19 @@
         <v>2412</v>
       </c>
     </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B350" t="n">
+        <v>62404386</v>
+      </c>
+      <c r="C350" t="n">
+        <v>2412</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/kpi-history.xlsx
+++ b/data/kpi-history.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C350"/>
+  <dimension ref="A1:C351"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -4986,6 +4986,19 @@
         <v>2412</v>
       </c>
     </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B351" t="n">
+        <v>62422318</v>
+      </c>
+      <c r="C351" t="n">
+        <v>2412</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/kpi-history.xlsx
+++ b/data/kpi-history.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C351"/>
+  <dimension ref="A1:C352"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -4999,6 +4999,19 @@
         <v>2412</v>
       </c>
     </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B352" t="n">
+        <v>62452687</v>
+      </c>
+      <c r="C352" t="n">
+        <v>2414</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/kpi-history.xlsx
+++ b/data/kpi-history.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C352"/>
+  <dimension ref="A1:C353"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -5012,6 +5012,19 @@
         <v>2414</v>
       </c>
     </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B353" t="n">
+        <v>62483193</v>
+      </c>
+      <c r="C353" t="n">
+        <v>2418</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/kpi-history.xlsx
+++ b/data/kpi-history.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C353"/>
+  <dimension ref="A1:C354"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -5025,6 +5025,19 @@
         <v>2418</v>
       </c>
     </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B354" t="n">
+        <v>62510036</v>
+      </c>
+      <c r="C354" t="n">
+        <v>2416</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/kpi-history.xlsx
+++ b/data/kpi-history.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C354"/>
+  <dimension ref="A1:C355"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -5038,6 +5038,19 @@
         <v>2416</v>
       </c>
     </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B355" t="n">
+        <v>62529755</v>
+      </c>
+      <c r="C355" t="n">
+        <v>2416</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/kpi-history.xlsx
+++ b/data/kpi-history.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C355"/>
+  <dimension ref="A1:C356"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -5051,6 +5051,19 @@
         <v>2416</v>
       </c>
     </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B356" t="n">
+        <v>62548387</v>
+      </c>
+      <c r="C356" t="n">
+        <v>2421</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/kpi-history.xlsx
+++ b/data/kpi-history.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C356"/>
+  <dimension ref="A1:C357"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -5064,6 +5064,19 @@
         <v>2421</v>
       </c>
     </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B357" t="n">
+        <v>62567431</v>
+      </c>
+      <c r="C357" t="n">
+        <v>2420</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/kpi-history.xlsx
+++ b/data/kpi-history.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C357"/>
+  <dimension ref="A1:C358"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -5077,6 +5077,19 @@
         <v>2420</v>
       </c>
     </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B358" t="n">
+        <v>62584718</v>
+      </c>
+      <c r="C358" t="n">
+        <v>2420</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/kpi-history.xlsx
+++ b/data/kpi-history.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C358"/>
+  <dimension ref="A1:C359"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -5090,6 +5090,19 @@
         <v>2420</v>
       </c>
     </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B359" t="n">
+        <v>62604668</v>
+      </c>
+      <c r="C359" t="n">
+        <v>2420</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/kpi-history.xlsx
+++ b/data/kpi-history.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C359"/>
+  <dimension ref="A1:C360"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -5103,6 +5103,19 @@
         <v>2420</v>
       </c>
     </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B360" t="n">
+        <v>62629997</v>
+      </c>
+      <c r="C360" t="n">
+        <v>2421</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/kpi-history.xlsx
+++ b/data/kpi-history.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C360"/>
+  <dimension ref="A1:C361"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -5116,6 +5116,19 @@
         <v>2421</v>
       </c>
     </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B361" t="n">
+        <v>62646031</v>
+      </c>
+      <c r="C361" t="n">
+        <v>2421</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/kpi-history.xlsx
+++ b/data/kpi-history.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C361"/>
+  <dimension ref="A1:C362"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -5129,6 +5129,19 @@
         <v>2421</v>
       </c>
     </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B362" t="n">
+        <v>62666503</v>
+      </c>
+      <c r="C362" t="n">
+        <v>2421</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/kpi-history.xlsx
+++ b/data/kpi-history.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C362"/>
+  <dimension ref="A1:C363"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -5142,6 +5142,19 @@
         <v>2421</v>
       </c>
     </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B363" t="n">
+        <v>62697640</v>
+      </c>
+      <c r="C363" t="n">
+        <v>2421</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/kpi-history.xlsx
+++ b/data/kpi-history.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C363"/>
+  <dimension ref="A1:C364"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -5155,6 +5155,19 @@
         <v>2421</v>
       </c>
     </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B364" t="n">
+        <v>62716001</v>
+      </c>
+      <c r="C364" t="n">
+        <v>2418</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/kpi-history.xlsx
+++ b/data/kpi-history.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C364"/>
+  <dimension ref="A1:C365"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -5168,6 +5168,19 @@
         <v>2418</v>
       </c>
     </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B365" t="n">
+        <v>62733812</v>
+      </c>
+      <c r="C365" t="n">
+        <v>2417</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/kpi-history.xlsx
+++ b/data/kpi-history.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C365"/>
+  <dimension ref="A1:C366"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -5181,6 +5181,19 @@
         <v>2417</v>
       </c>
     </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B366" t="n">
+        <v>62756808</v>
+      </c>
+      <c r="C366" t="n">
+        <v>2416</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/kpi-history.xlsx
+++ b/data/kpi-history.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C366"/>
+  <dimension ref="A1:C367"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -5194,6 +5194,19 @@
         <v>2416</v>
       </c>
     </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B367" t="n">
+        <v>62779408</v>
+      </c>
+      <c r="C367" t="n">
+        <v>2419</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/kpi-history.xlsx
+++ b/data/kpi-history.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C367"/>
+  <dimension ref="A1:C368"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -5207,6 +5207,19 @@
         <v>2419</v>
       </c>
     </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B368" t="n">
+        <v>62802919</v>
+      </c>
+      <c r="C368" t="n">
+        <v>2414</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/kpi-history.xlsx
+++ b/data/kpi-history.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C368"/>
+  <dimension ref="A1:C369"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -5220,6 +5220,19 @@
         <v>2414</v>
       </c>
     </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B369" t="n">
+        <v>62837545</v>
+      </c>
+      <c r="C369" t="n">
+        <v>2411</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/kpi-history.xlsx
+++ b/data/kpi-history.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C369"/>
+  <dimension ref="A1:C370"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -5233,6 +5233,19 @@
         <v>2411</v>
       </c>
     </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B370" t="n">
+        <v>62879471</v>
+      </c>
+      <c r="C370" t="n">
+        <v>2406</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/kpi-history.xlsx
+++ b/data/kpi-history.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C370"/>
+  <dimension ref="A1:C371"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -5246,6 +5246,19 @@
         <v>2406</v>
       </c>
     </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B371" t="n">
+        <v>62903237</v>
+      </c>
+      <c r="C371" t="n">
+        <v>2404</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/kpi-history.xlsx
+++ b/data/kpi-history.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C371"/>
+  <dimension ref="A1:C372"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -5259,6 +5259,19 @@
         <v>2404</v>
       </c>
     </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B372" t="n">
+        <v>62923339</v>
+      </c>
+      <c r="C372" t="n">
+        <v>2404</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/kpi-history.xlsx
+++ b/data/kpi-history.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C372"/>
+  <dimension ref="A1:C373"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -5272,6 +5272,19 @@
         <v>2404</v>
       </c>
     </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B373" t="n">
+        <v>62961107</v>
+      </c>
+      <c r="C373" t="n">
+        <v>2401</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/kpi-history.xlsx
+++ b/data/kpi-history.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C373"/>
+  <dimension ref="A1:C374"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -5285,6 +5285,19 @@
         <v>2401</v>
       </c>
     </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B374" t="n">
+        <v>63012255</v>
+      </c>
+      <c r="C374" t="n">
+        <v>2403</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/kpi-history.xlsx
+++ b/data/kpi-history.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C374"/>
+  <dimension ref="A1:C375"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -5298,6 +5298,19 @@
         <v>2403</v>
       </c>
     </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B375" t="n">
+        <v>63034127</v>
+      </c>
+      <c r="C375" t="n">
+        <v>2401</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/kpi-history.xlsx
+++ b/data/kpi-history.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C375"/>
+  <dimension ref="A1:C376"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -5311,6 +5311,19 @@
         <v>2401</v>
       </c>
     </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B376" t="n">
+        <v>63054014</v>
+      </c>
+      <c r="C376" t="n">
+        <v>2400</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/kpi-history.xlsx
+++ b/data/kpi-history.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C376"/>
+  <dimension ref="A1:C377"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -5324,6 +5324,19 @@
         <v>2400</v>
       </c>
     </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B377" t="n">
+        <v>63079102</v>
+      </c>
+      <c r="C377" t="n">
+        <v>2399</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/kpi-history.xlsx
+++ b/data/kpi-history.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C377"/>
+  <dimension ref="A1:C378"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -5337,6 +5337,19 @@
         <v>2399</v>
       </c>
     </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B378" t="n">
+        <v>63103719</v>
+      </c>
+      <c r="C378" t="n">
+        <v>2402</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/kpi-history.xlsx
+++ b/data/kpi-history.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C378"/>
+  <dimension ref="A1:C379"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -5350,6 +5350,19 @@
         <v>2402</v>
       </c>
     </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B379" t="n">
+        <v>63125133</v>
+      </c>
+      <c r="C379" t="n">
+        <v>2402</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/kpi-history.xlsx
+++ b/data/kpi-history.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C379"/>
+  <dimension ref="A1:C380"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -5363,6 +5363,19 @@
         <v>2402</v>
       </c>
     </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B380" t="n">
+        <v>63149359</v>
+      </c>
+      <c r="C380" t="n">
+        <v>2400</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/kpi-history.xlsx
+++ b/data/kpi-history.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C380"/>
+  <dimension ref="A1:C381"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -5376,6 +5376,19 @@
         <v>2400</v>
       </c>
     </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B381" t="n">
+        <v>63170702</v>
+      </c>
+      <c r="C381" t="n">
+        <v>2400</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/kpi-history.xlsx
+++ b/data/kpi-history.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C381"/>
+  <dimension ref="A1:C382"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -5389,6 +5389,19 @@
         <v>2400</v>
       </c>
     </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B382" t="n">
+        <v>63198547</v>
+      </c>
+      <c r="C382" t="n">
+        <v>2405</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/kpi-history.xlsx
+++ b/data/kpi-history.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C382"/>
+  <dimension ref="A1:C383"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -5402,6 +5402,19 @@
         <v>2405</v>
       </c>
     </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B383" t="n">
+        <v>63239628</v>
+      </c>
+      <c r="C383" t="n">
+        <v>2415</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/kpi-history.xlsx
+++ b/data/kpi-history.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C383"/>
+  <dimension ref="A1:C384"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -5415,6 +5415,19 @@
         <v>2415</v>
       </c>
     </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="B384" t="n">
+        <v>63264153</v>
+      </c>
+      <c r="C384" t="n">
+        <v>2417</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/kpi-history.xlsx
+++ b/data/kpi-history.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C384"/>
+  <dimension ref="A1:C385"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -5428,6 +5428,19 @@
         <v>2417</v>
       </c>
     </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="B385" t="n">
+        <v>63292031</v>
+      </c>
+      <c r="C385" t="n">
+        <v>2415</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/kpi-history.xlsx
+++ b/data/kpi-history.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C385"/>
+  <dimension ref="A1:C386"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -5441,6 +5441,19 @@
         <v>2415</v>
       </c>
     </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B386" t="n">
+        <v>63311310</v>
+      </c>
+      <c r="C386" t="n">
+        <v>2415</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/kpi-history.xlsx
+++ b/data/kpi-history.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C386"/>
+  <dimension ref="A1:C387"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -5454,6 +5454,19 @@
         <v>2415</v>
       </c>
     </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B387" t="n">
+        <v>63331025</v>
+      </c>
+      <c r="C387" t="n">
+        <v>2414</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/kpi-history.xlsx
+++ b/data/kpi-history.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C387"/>
+  <dimension ref="A1:C388"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -5467,6 +5467,19 @@
         <v>2414</v>
       </c>
     </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B388" t="n">
+        <v>63355345</v>
+      </c>
+      <c r="C388" t="n">
+        <v>2414</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/kpi-history.xlsx
+++ b/data/kpi-history.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C388"/>
+  <dimension ref="A1:C389"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -5480,6 +5480,19 @@
         <v>2414</v>
       </c>
     </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B389" t="n">
+        <v>63380407</v>
+      </c>
+      <c r="C389" t="n">
+        <v>2413</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/kpi-history.xlsx
+++ b/data/kpi-history.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C389"/>
+  <dimension ref="A1:C390"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -5493,6 +5493,19 @@
         <v>2413</v>
       </c>
     </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B390" t="n">
+        <v>63399181</v>
+      </c>
+      <c r="C390" t="n">
+        <v>2413</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/kpi-history.xlsx
+++ b/data/kpi-history.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C390"/>
+  <dimension ref="A1:C393"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -5506,6 +5506,45 @@
         <v>2413</v>
       </c>
     </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B391" t="n">
+        <v>63426993</v>
+      </c>
+      <c r="C391" t="n">
+        <v>2414</v>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="B392" t="n">
+        <v>63450681</v>
+      </c>
+      <c r="C392" t="n">
+        <v>2415</v>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B393" t="n">
+        <v>63486014</v>
+      </c>
+      <c r="C393" t="n">
+        <v>2413</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/kpi-history.xlsx
+++ b/data/kpi-history.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C393"/>
+  <dimension ref="A1:C394"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -5545,6 +5545,19 @@
         <v>2413</v>
       </c>
     </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B394" t="n">
+        <v>63509411</v>
+      </c>
+      <c r="C394" t="n">
+        <v>2417</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/kpi-history.xlsx
+++ b/data/kpi-history.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C394"/>
+  <dimension ref="A1:C395"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -5558,6 +5558,19 @@
         <v>2417</v>
       </c>
     </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B395" t="n">
+        <v>63514550</v>
+      </c>
+      <c r="C395" t="n">
+        <v>2417</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/kpi-history.xlsx
+++ b/data/kpi-history.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C395"/>
+  <dimension ref="A1:C396"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -5571,6 +5571,19 @@
         <v>2417</v>
       </c>
     </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B396" t="n">
+        <v>63543346</v>
+      </c>
+      <c r="C396" t="n">
+        <v>2420</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/kpi-history.xlsx
+++ b/data/kpi-history.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C396"/>
+  <dimension ref="A1:C397"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -5584,6 +5584,19 @@
         <v>2420</v>
       </c>
     </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B397" t="n">
+        <v>63568503</v>
+      </c>
+      <c r="C397" t="n">
+        <v>2422</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/kpi-history.xlsx
+++ b/data/kpi-history.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C397"/>
+  <dimension ref="A1:C398"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -5597,6 +5597,19 @@
         <v>2422</v>
       </c>
     </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="B398" t="n">
+        <v>63601648</v>
+      </c>
+      <c r="C398" t="n">
+        <v>2413</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
